--- a/data/trans_orig/P41E_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P41E_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si con respecto al último año sus relaciones sexuales han sido satisfactorias para ambas partes en 2023</t>
+          <t>Población según si con respecto al último año sus relaciones sexuales han sido satisfactorias para ambas partes en 2023 (tasa de respuesta: 69,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1804</t>
+          <t>1798</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16704</t>
+          <t>17241</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1032</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9732</t>
+          <t>9657</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4419</t>
+          <t>4014</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21416</t>
+          <t>21008</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,72%</t>
         </is>
       </c>
     </row>
@@ -843,97 +843,97 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>3406</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>3730</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>11502</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>4,27%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>3,75%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>14,42%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>3406</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>11093</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>4,27%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>10659</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>13,91%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>3406</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>12397</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>1,9%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8456</t>
+          <t>8118</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27832</t>
+          <t>27914</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5717</t>
+          <t>4940</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21591</t>
+          <t>20171</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>17077</t>
+          <t>18022</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>42724</t>
+          <t>42646</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,8%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9746</t>
+          <t>9841</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33455</t>
+          <t>33303</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11272</t>
+          <t>12955</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32917</t>
+          <t>32750</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25221</t>
+          <t>26000</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>56737</t>
+          <t>57456</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>32,06%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>41169</t>
+          <t>40475</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>70721</t>
+          <t>71393</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>28489</t>
+          <t>28700</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>51251</t>
+          <t>51028</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>63,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>77523</t>
+          <t>76780</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>115387</t>
+          <t>116025</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,39%</t>
+          <t>64,75%</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8872</t>
+          <t>11339</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>879</t>
+          <t>881</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9361</t>
+          <t>8843</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2119</t>
+          <t>2148</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13077</t>
+          <t>13364</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6175</t>
+          <t>5728</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6821</t>
+          <t>6350</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7290</t>
+          <t>7373</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4729</t>
+          <t>4245</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18536</t>
+          <t>18373</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3638</t>
+          <t>3457</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>14318</t>
+          <t>14736</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>10462</t>
+          <t>10336</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>28723</t>
+          <t>27808</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,08%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31488</t>
+          <t>31088</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>63324</t>
+          <t>62080</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>41176</t>
+          <t>40182</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>65229</t>
+          <t>64528</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>80313</t>
+          <t>79831</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>117758</t>
+          <t>117220</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>29,86%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>114358</t>
+          <t>114131</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>147883</t>
+          <t>147658</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>59,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,02%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>122971</t>
+          <t>123938</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>149081</t>
+          <t>149832</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>61,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>74,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>247923</t>
+          <t>249195</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>289921</t>
+          <t>288722</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>63,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,86%</t>
+          <t>73,55%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8733</t>
+          <t>8923</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>515</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6233</t>
+          <t>5756</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2394</t>
+          <t>2621</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11605</t>
+          <t>11211</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>785</t>
+          <t>803</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7538</t>
+          <t>7172</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1602</t>
+          <t>1448</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8858</t>
+          <t>8813</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3682</t>
+          <t>3576</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13095</t>
+          <t>13133</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7877</t>
+          <t>8191</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>23787</t>
+          <t>23394</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6017</t>
+          <t>6424</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16338</t>
+          <t>16391</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>16285</t>
+          <t>16980</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>34204</t>
+          <t>35404</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>93117</t>
+          <t>91717</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>126156</t>
+          <t>125381</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>93140</t>
+          <t>92034</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>118858</t>
+          <t>118072</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>194656</t>
+          <t>192391</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>235750</t>
+          <t>235581</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>41,36%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>143078</t>
+          <t>142670</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>178124</t>
+          <t>177219</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>49,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>61,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>144644</t>
+          <t>144496</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>171116</t>
+          <t>170696</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,73%</t>
+          <t>51,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>61,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>294588</t>
+          <t>297156</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>337630</t>
+          <t>340906</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>51,72%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>59,28%</t>
+          <t>59,85%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1693</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17406</t>
+          <t>17500</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7610</t>
+          <t>7663</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19067</t>
+          <t>18446</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6858</t>
+          <t>7977</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>30499</t>
+          <t>31065</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1482</t>
+          <t>1246</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>19638</t>
+          <t>19623</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>6744</t>
+          <t>7004</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>18272</t>
+          <t>17458</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>8345</t>
+          <t>8152</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>32090</t>
+          <t>32527</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5856</t>
+          <t>5353</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>42389</t>
+          <t>42190</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>23155</t>
+          <t>23854</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>40801</t>
+          <t>40156</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>21890</t>
+          <t>23917</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>77274</t>
+          <t>76089</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,34%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>36273</t>
+          <t>38689</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>201328</t>
+          <t>205303</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>116559</t>
+          <t>116276</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>144144</t>
+          <t>143780</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>96555</t>
+          <t>113693</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>333253</t>
+          <t>331534</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,32%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>283806</t>
+          <t>281954</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>505599</t>
+          <t>507376</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>50,97%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>161900</t>
+          <t>161397</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>190483</t>
+          <t>190889</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>53,07%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>456261</t>
+          <t>455559</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>775484</t>
+          <t>751214</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>49,91%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>82,29%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>21746</t>
+          <t>22647</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>40255</t>
+          <t>39914</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>22572</t>
+          <t>23719</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>39226</t>
+          <t>38041</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>50986</t>
+          <t>50879</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>75780</t>
+          <t>75322</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,57%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>11208</t>
+          <t>11388</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>25051</t>
+          <t>27279</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>12874</t>
+          <t>13204</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>25726</t>
+          <t>25310</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>26492</t>
+          <t>27607</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>46382</t>
+          <t>46447</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,75%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>32972</t>
+          <t>31905</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>54708</t>
+          <t>54588</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>34409</t>
+          <t>35257</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>52531</t>
+          <t>52999</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>72210</t>
+          <t>71914</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>102233</t>
+          <t>99926</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,68%</t>
         </is>
       </c>
     </row>
@@ -3797,7 +3797,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>89615</t>
+          <t>90137</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>73338</t>
+          <t>72353</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>95861</t>
+          <t>95402</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>170807</t>
+          <t>168825</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>208683</t>
+          <t>208033</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>34,72%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>106749</t>
+          <t>106176</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>139197</t>
+          <t>137901</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>95088</t>
+          <t>93891</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>118794</t>
+          <t>118760</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>41,95%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>207078</t>
+          <t>207674</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>247667</t>
+          <t>248216</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>41,42%</t>
         </is>
       </c>
     </row>
@@ -4140,12 +4140,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>20859</t>
+          <t>21275</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>36202</t>
+          <t>36456</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4175,12 +4175,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>8256</t>
+          <t>8214</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>76427</t>
+          <t>76684</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>21979</t>
+          <t>21455</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>98158</t>
+          <t>97204</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,58%</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>15826</t>
+          <t>15991</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>30104</t>
+          <t>29639</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3642</t>
+          <t>3267</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>38859</t>
+          <t>40303</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>13800</t>
+          <t>14104</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>64136</t>
+          <t>64110</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>18548</t>
+          <t>19485</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>33836</t>
+          <t>33969</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>8425</t>
+          <t>8730</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>77484</t>
+          <t>78023</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>20167</t>
+          <t>20896</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>95800</t>
+          <t>94253</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,05%</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>47035</t>
+          <t>46600</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>67199</t>
+          <t>66407</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>9036</t>
+          <t>7957</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>82787</t>
+          <t>83697</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>34942</t>
+          <t>34182</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>148643</t>
+          <t>148591</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,88%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>54603</t>
+          <t>55474</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>76388</t>
+          <t>76134</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>92199</t>
+          <t>90838</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>323618</t>
+          <t>326784</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>162079</t>
+          <t>164097</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>458002</t>
+          <t>459124</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>83,05%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>21665</t>
+          <t>20905</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>35123</t>
+          <t>35341</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>34253</t>
+          <t>34449</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>47284</t>
+          <t>48342</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>44,15%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>58985</t>
+          <t>58426</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>78107</t>
+          <t>78598</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,76%</t>
         </is>
       </c>
     </row>
@@ -4935,12 +4935,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>9190</t>
+          <t>9167</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>20078</t>
+          <t>19998</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>3695</t>
+          <t>3578</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>10488</t>
+          <t>11202</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>14677</t>
+          <t>15126</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>27394</t>
+          <t>28098</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,78%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>16845</t>
+          <t>16353</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>29419</t>
+          <t>29696</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>27294</t>
+          <t>26768</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>39856</t>
+          <t>40201</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>47033</t>
+          <t>46436</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>64590</t>
+          <t>65748</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,91%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>19676</t>
+          <t>18965</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>34094</t>
+          <t>34137</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>9868</t>
+          <t>9741</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>19662</t>
+          <t>19900</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>32395</t>
+          <t>31995</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>49774</t>
+          <t>49465</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,5%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>14559</t>
+          <t>14491</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>27321</t>
+          <t>27733</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>10269</t>
+          <t>10724</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>20453</t>
+          <t>20635</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>27750</t>
+          <t>27580</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>44621</t>
+          <t>43133</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>19,62%</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>64115</t>
+          <t>66021</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>132696</t>
+          <t>134859</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>82298</t>
+          <t>76296</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>146997</t>
+          <t>146786</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>176937</t>
+          <t>172926</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>269334</t>
+          <t>269810</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,88%</t>
         </is>
       </c>
     </row>
@@ -5617,12 +5617,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>39620</t>
+          <t>42588</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>84648</t>
+          <t>84869</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5632,12 +5632,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>38092</t>
+          <t>40239</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>76549</t>
+          <t>76625</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>96351</t>
+          <t>93737</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>153837</t>
+          <t>152135</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -5730,12 +5730,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>93251</t>
+          <t>95933</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>185680</t>
+          <t>189898</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5745,12 +5745,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5765,12 +5765,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>107609</t>
+          <t>106968</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>199222</t>
+          <t>197019</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>239826</t>
+          <t>236783</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>369225</t>
+          <t>367288</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,72%</t>
         </is>
       </c>
     </row>
@@ -5843,12 +5843,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>291134</t>
+          <t>294676</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>559499</t>
+          <t>559933</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5858,12 +5858,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>295654</t>
+          <t>289168</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>510895</t>
+          <t>511166</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>688219</t>
+          <t>678010</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>1042641</t>
+          <t>1041990</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,41%</t>
         </is>
       </c>
     </row>
@@ -5956,12 +5956,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>822842</t>
+          <t>817951</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>1261126</t>
+          <t>1251991</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>71,19%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5991,12 +5991,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>758941</t>
+          <t>754114</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>1136916</t>
+          <t>1165183</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6006,12 +6006,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>69,88%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6026,12 +6026,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>1612295</t>
+          <t>1606545</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>2225227</t>
+          <t>2231183</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>64,95%</t>
+          <t>65,13%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P41E_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P41E_2023-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>7117</t>
+          <t>6068</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1798</t>
+          <t>1631</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17241</t>
+          <t>14710</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3810</t>
+          <t>3851</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9657</t>
+          <t>10388</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>10928</t>
+          <t>9919</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4014</t>
+          <t>3996</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21008</t>
+          <t>18413</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>9,95%</t>
         </is>
       </c>
     </row>
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>3786</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11502</t>
+          <t>13297</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>3786</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10659</t>
+          <t>11560</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16433</t>
+          <t>16051</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8118</t>
+          <t>8959</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27914</t>
+          <t>27069</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>11851</t>
+          <t>13651</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4940</t>
+          <t>6537</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20171</t>
+          <t>23918</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>28284</t>
+          <t>29701</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>18022</t>
+          <t>17982</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>42646</t>
+          <t>43814</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,67%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18710</t>
+          <t>18300</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9841</t>
+          <t>9481</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33303</t>
+          <t>32308</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21119</t>
+          <t>24641</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12955</t>
+          <t>15393</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32750</t>
+          <t>37457</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>39829</t>
+          <t>42940</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>29123</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>57456</t>
+          <t>61519</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>33,23%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>57194</t>
+          <t>57317</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>40475</t>
+          <t>43421</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>71393</t>
+          <t>70874</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>44,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>39556</t>
+          <t>41461</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>28700</t>
+          <t>28601</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>51028</t>
+          <t>53878</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>47,44%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,99%</t>
+          <t>61,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>96750</t>
+          <t>98777</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>76780</t>
+          <t>80446</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>116025</t>
+          <t>118114</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>53,99%</t>
+          <t>53,36%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>63,8%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>99454</t>
+          <t>97735</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>99454</t>
+          <t>97735</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>99454</t>
+          <t>97735</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>79742</t>
+          <t>87389</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>79742</t>
+          <t>87389</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>79742</t>
+          <t>87389</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>179196</t>
+          <t>185123</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>179196</t>
+          <t>185123</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>179196</t>
+          <t>185123</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2898</t>
+          <t>2951</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11339</t>
+          <t>9270</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3024</t>
+          <t>2871</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>850</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8843</t>
+          <t>8543</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>5923</t>
+          <t>5822</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2148</t>
+          <t>1913</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13364</t>
+          <t>14132</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1192</t>
+          <t>1311</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5728</t>
+          <t>7090</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1123</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6350</t>
+          <t>5136</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2316</t>
+          <t>2326</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7373</t>
+          <t>7987</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9919</t>
+          <t>15714</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4245</t>
+          <t>7750</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18373</t>
+          <t>27881</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7735</t>
+          <t>7966</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3457</t>
+          <t>3620</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>14736</t>
+          <t>14951</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>17654</t>
+          <t>23681</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>10336</t>
+          <t>14279</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>27808</t>
+          <t>37878</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>8,56%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>45399</t>
+          <t>50523</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31088</t>
+          <t>35969</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>62080</t>
+          <t>69682</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>52268</t>
+          <t>66862</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40182</t>
+          <t>52691</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>64528</t>
+          <t>81212</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>97667</t>
+          <t>117386</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>79831</t>
+          <t>97464</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>117220</t>
+          <t>137911</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>31,15%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>132597</t>
+          <t>146226</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>114131</t>
+          <t>127529</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>147658</t>
+          <t>164353</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>67,47%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>58,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>75,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>136386</t>
+          <t>147241</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>123938</t>
+          <t>132916</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>149832</t>
+          <t>160554</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>65,16%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>58,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>268982</t>
+          <t>293466</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>249195</t>
+          <t>269122</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>288722</t>
+          <t>317557</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>66,29%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>60,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,55%</t>
+          <t>71,73%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>192005</t>
+          <t>216725</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>192005</t>
+          <t>216725</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>192005</t>
+          <t>216725</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>200537</t>
+          <t>225956</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>200537</t>
+          <t>225956</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>200537</t>
+          <t>225956</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>392542</t>
+          <t>442681</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>392542</t>
+          <t>442681</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>392542</t>
+          <t>442681</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>4763</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1666</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8923</t>
+          <t>11134</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2174</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>596</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5756</t>
+          <t>6395</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>5835</t>
+          <t>7090</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2621</t>
+          <t>3325</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11211</t>
+          <t>13681</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3070</t>
+          <t>3096</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>803</t>
+          <t>786</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7172</t>
+          <t>7679</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4259</t>
+          <t>4387</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1448</t>
+          <t>1588</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8813</t>
+          <t>9468</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>7330</t>
+          <t>7484</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3576</t>
+          <t>3805</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13133</t>
+          <t>13738</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>14297</t>
+          <t>18049</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8191</t>
+          <t>10700</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>23394</t>
+          <t>27874</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>10316</t>
+          <t>11321</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6424</t>
+          <t>6529</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16391</t>
+          <t>17952</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>24613</t>
+          <t>29370</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>16980</t>
+          <t>19837</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>35404</t>
+          <t>41153</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,3%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>108318</t>
+          <t>124604</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>91717</t>
+          <t>106949</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>125381</t>
+          <t>143648</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>105157</t>
+          <t>120983</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>92034</t>
+          <t>106195</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>118072</t>
+          <t>137105</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>213475</t>
+          <t>245587</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>192391</t>
+          <t>221165</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>235581</t>
+          <t>267436</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>40,97%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>160623</t>
+          <t>183293</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>142670</t>
+          <t>164932</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>177219</t>
+          <t>202395</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>54,91%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>49,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>61,12%</t>
+          <t>60,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>157691</t>
+          <t>179993</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>144496</t>
+          <t>163458</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>170696</t>
+          <t>194913</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>56,4%</t>
+          <t>56,42%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>61,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>318314</t>
+          <t>363286</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>297156</t>
+          <t>342070</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>340906</t>
+          <t>388990</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>55,65%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>52,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>59,59%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>289970</t>
+          <t>333805</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>289970</t>
+          <t>333805</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>289970</t>
+          <t>333805</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>279597</t>
+          <t>319011</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>279597</t>
+          <t>319011</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>279597</t>
+          <t>319011</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>569567</t>
+          <t>652816</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>569567</t>
+          <t>652816</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>569567</t>
+          <t>652816</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>7824</t>
+          <t>8178</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>3998</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17500</t>
+          <t>13548</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>11919</t>
+          <t>12295</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7663</t>
+          <t>7587</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18446</t>
+          <t>19388</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>19743</t>
+          <t>20473</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7977</t>
+          <t>13848</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>31065</t>
+          <t>28707</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>8681</t>
+          <t>8953</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>4572</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>19623</t>
+          <t>16484</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>11192</t>
+          <t>12050</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>7004</t>
+          <t>7298</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>17458</t>
+          <t>18526</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>19874</t>
+          <t>21004</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>8152</t>
+          <t>13380</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>32527</t>
+          <t>30500</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>21291</t>
+          <t>22238</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5353</t>
+          <t>15260</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>42190</t>
+          <t>33049</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>30610</t>
+          <t>32423</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>23854</t>
+          <t>24622</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>40156</t>
+          <t>41977</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>51901</t>
+          <t>54660</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>23917</t>
+          <t>42635</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>76089</t>
+          <t>67414</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>9,37%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>107957</t>
+          <t>119558</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>38689</t>
+          <t>102116</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>205303</t>
+          <t>137169</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>41,16%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>129976</t>
+          <t>141972</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>116276</t>
+          <t>127940</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>143780</t>
+          <t>157173</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>237933</t>
+          <t>261530</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>113693</t>
+          <t>239471</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>331534</t>
+          <t>284024</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>39,48%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>407410</t>
+          <t>174352</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>281954</t>
+          <t>156286</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>507376</t>
+          <t>193205</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>52,31%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>57,97%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>175977</t>
+          <t>187346</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>161397</t>
+          <t>172098</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>190889</t>
+          <t>203514</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>48,52%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>44,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>52,71%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>583387</t>
+          <t>361698</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>455559</t>
+          <t>338840</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>751214</t>
+          <t>387704</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>47,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>53,9%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>553163</t>
+          <t>333279</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>553163</t>
+          <t>333279</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>553163</t>
+          <t>333279</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>359675</t>
+          <t>386086</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>359675</t>
+          <t>386086</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>359675</t>
+          <t>386086</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>912838</t>
+          <t>719364</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>912838</t>
+          <t>719364</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>912838</t>
+          <t>719364</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,32 +3453,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>30704</t>
+          <t>32587</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>22647</t>
+          <t>23711</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>39914</t>
+          <t>43918</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,32 +3488,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>30650</t>
+          <t>35023</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>23719</t>
+          <t>26677</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>38041</t>
+          <t>44348</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>61354</t>
+          <t>67610</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>50879</t>
+          <t>56313</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>75322</t>
+          <t>81683</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,41%</t>
         </is>
       </c>
     </row>
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>17595</t>
+          <t>18825</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>11388</t>
+          <t>12058</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>27279</t>
+          <t>27951</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,17 +3601,17 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>18668</t>
+          <t>20867</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>13204</t>
+          <t>14588</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>25310</t>
+          <t>28830</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>36264</t>
+          <t>39692</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>27607</t>
+          <t>30568</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>46447</t>
+          <t>51311</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,8%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>42299</t>
+          <t>44673</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>31905</t>
+          <t>32445</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>54588</t>
+          <t>56586</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>43305</t>
+          <t>48359</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>35257</t>
+          <t>39181</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>52999</t>
+          <t>59012</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>85604</t>
+          <t>93032</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>71914</t>
+          <t>78379</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>99926</t>
+          <t>109388</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,62%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>104443</t>
+          <t>117097</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>90137</t>
+          <t>100467</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>119730</t>
+          <t>133671</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>39,18%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>84258</t>
+          <t>96557</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>72353</t>
+          <t>83663</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>95402</t>
+          <t>107863</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>188701</t>
+          <t>213654</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>168825</t>
+          <t>193563</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>208033</t>
+          <t>236243</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>35,9%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>121087</t>
+          <t>127988</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>106176</t>
+          <t>112279</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>137901</t>
+          <t>145541</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>106210</t>
+          <t>116054</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>93891</t>
+          <t>103225</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>118760</t>
+          <t>129664</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>227296</t>
+          <t>244042</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>207674</t>
+          <t>221428</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>248216</t>
+          <t>263929</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>40,11%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>316128</t>
+          <t>341170</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>316128</t>
+          <t>341170</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>316128</t>
+          <t>341170</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>283091</t>
+          <t>316859</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>283091</t>
+          <t>316859</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>283091</t>
+          <t>316859</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>599219</t>
+          <t>658029</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>599219</t>
+          <t>658029</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>599219</t>
+          <t>658029</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4135,32 +4135,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>27685</t>
+          <t>30458</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>21275</t>
+          <t>22978</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>36456</t>
+          <t>39455</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4170,32 +4170,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>30285</t>
+          <t>33082</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>8214</t>
+          <t>26233</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>76684</t>
+          <t>41198</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>57970</t>
+          <t>63540</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>21455</t>
+          <t>53157</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>97204</t>
+          <t>75181</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>19,7%</t>
         </is>
       </c>
     </row>
@@ -4248,32 +4248,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>22453</t>
+          <t>24418</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>15991</t>
+          <t>17620</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>29639</t>
+          <t>33284</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>15089</t>
+          <t>17243</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3267</t>
+          <t>11794</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>40303</t>
+          <t>23509</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>37543</t>
+          <t>41661</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>14104</t>
+          <t>33124</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>64110</t>
+          <t>52440</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>13,74%</t>
         </is>
       </c>
     </row>
@@ -4361,32 +4361,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>25610</t>
+          <t>27851</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>19485</t>
+          <t>21070</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>33969</t>
+          <t>36508</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4396,32 +4396,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>30699</t>
+          <t>32344</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>8730</t>
+          <t>25600</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>78023</t>
+          <t>40711</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>56309</t>
+          <t>60195</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>20896</t>
+          <t>49592</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>94253</t>
+          <t>71247</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>18,67%</t>
         </is>
       </c>
     </row>
@@ -4474,32 +4474,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>56425</t>
+          <t>64105</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>46600</t>
+          <t>52971</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>66407</t>
+          <t>75448</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4509,32 +4509,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>33057</t>
+          <t>36147</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>7957</t>
+          <t>28170</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>83697</t>
+          <t>44110</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>89482</t>
+          <t>100252</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>34182</t>
+          <t>86986</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>148591</t>
+          <t>115097</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>30,16%</t>
         </is>
       </c>
     </row>
@@ -4587,32 +4587,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>65455</t>
+          <t>70135</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>55474</t>
+          <t>59047</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>76134</t>
+          <t>82371</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4622,32 +4622,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>246050</t>
+          <t>45828</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>90838</t>
+          <t>38092</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>326784</t>
+          <t>54495</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>311505</t>
+          <t>115963</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>164097</t>
+          <t>103044</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>459124</t>
+          <t>131972</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>34,58%</t>
         </is>
       </c>
     </row>
@@ -4700,17 +4700,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>197628</t>
+          <t>216967</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>197628</t>
+          <t>216967</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>197628</t>
+          <t>216967</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>355181</t>
+          <t>164643</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>355181</t>
+          <t>164643</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>355181</t>
+          <t>164643</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>552809</t>
+          <t>381610</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>552809</t>
+          <t>381610</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>552809</t>
+          <t>381610</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4817,32 +4817,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>27445</t>
+          <t>29082</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>20905</t>
+          <t>22757</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>35341</t>
+          <t>37112</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4852,32 +4852,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>40824</t>
+          <t>44445</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>34449</t>
+          <t>37250</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>48342</t>
+          <t>51960</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>44,02%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>68270</t>
+          <t>73527</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>58426</t>
+          <t>62712</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>78598</t>
+          <t>84515</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,62%</t>
         </is>
       </c>
     </row>
@@ -4930,32 +4930,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>14043</t>
+          <t>15736</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>9167</t>
+          <t>10172</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>19998</t>
+          <t>21867</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>6681</t>
+          <t>7396</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>3578</t>
+          <t>4217</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>11202</t>
+          <t>12574</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>20724</t>
+          <t>23132</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>15126</t>
+          <t>16867</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>28098</t>
+          <t>31484</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>13,27%</t>
         </is>
       </c>
     </row>
@@ -5043,32 +5043,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>23696</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>16353</t>
+          <t>17386</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>29696</t>
+          <t>31184</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5078,32 +5078,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>32987</t>
+          <t>34855</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>26768</t>
+          <t>27660</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>40201</t>
+          <t>42326</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>55567</t>
+          <t>58550</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>46436</t>
+          <t>49072</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>65748</t>
+          <t>68700</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>28,95%</t>
         </is>
       </c>
     </row>
@@ -5156,32 +5156,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>26081</t>
+          <t>29839</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>18965</t>
+          <t>22463</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>34137</t>
+          <t>38485</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5191,32 +5191,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>14110</t>
+          <t>15619</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>9741</t>
+          <t>10518</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>19900</t>
+          <t>21053</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>40192</t>
+          <t>45458</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>31995</t>
+          <t>36414</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>49465</t>
+          <t>56660</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>23,88%</t>
         </is>
       </c>
     </row>
@@ -5269,32 +5269,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>20161</t>
+          <t>20905</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>14491</t>
+          <t>14010</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>27733</t>
+          <t>27678</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5304,32 +5304,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>14883</t>
+          <t>15720</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>10724</t>
+          <t>10999</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>20635</t>
+          <t>21898</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>35044</t>
+          <t>36625</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>27580</t>
+          <t>29140</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>43133</t>
+          <t>45806</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,3%</t>
         </is>
       </c>
     </row>
@@ -5382,17 +5382,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>110312</t>
+          <t>119258</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>110312</t>
+          <t>119258</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>110312</t>
+          <t>119258</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5417,17 +5417,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>109485</t>
+          <t>118034</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>109485</t>
+          <t>118034</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>109485</t>
+          <t>118034</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>219797</t>
+          <t>237292</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>219797</t>
+          <t>237292</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>219797</t>
+          <t>237292</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5499,32 +5499,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>107335</t>
+          <t>114086</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>66021</t>
+          <t>96482</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>134859</t>
+          <t>133023</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5534,32 +5534,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>122688</t>
+          <t>133895</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>76296</t>
+          <t>117722</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>146786</t>
+          <t>152309</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5569,32 +5569,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>230023</t>
+          <t>247981</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>172926</t>
+          <t>223971</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>269810</t>
+          <t>275122</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,4%</t>
         </is>
       </c>
     </row>
@@ -5612,32 +5612,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>67036</t>
+          <t>72339</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>42588</t>
+          <t>58025</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>84869</t>
+          <t>86950</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5647,32 +5647,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>60419</t>
+          <t>66744</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>40239</t>
+          <t>53818</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>76625</t>
+          <t>79844</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5682,32 +5682,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>127455</t>
+          <t>139083</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>93737</t>
+          <t>121019</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>152135</t>
+          <t>161332</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -5725,32 +5725,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>152429</t>
+          <t>168271</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>95933</t>
+          <t>143513</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>189898</t>
+          <t>189431</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5760,32 +5760,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>167503</t>
+          <t>180917</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>106968</t>
+          <t>159847</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>197019</t>
+          <t>201626</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5795,32 +5795,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>319932</t>
+          <t>349189</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>236783</t>
+          <t>317876</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>367288</t>
+          <t>381411</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>11,64%</t>
         </is>
       </c>
     </row>
@@ -5838,32 +5838,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>467334</t>
+          <t>524027</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>294676</t>
+          <t>485206</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>559933</t>
+          <t>563621</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5873,32 +5873,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>439945</t>
+          <t>502780</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>289168</t>
+          <t>471577</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>511166</t>
+          <t>532257</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5908,32 +5908,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>907279</t>
+          <t>1026807</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>678010</t>
+          <t>977498</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>1041990</t>
+          <t>1079154</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>32,93%</t>
         </is>
       </c>
     </row>
@@ -5951,32 +5951,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>964527</t>
+          <t>780215</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>817951</t>
+          <t>737074</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>1251991</t>
+          <t>821380</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>44,43%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>49,51%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5986,32 +5986,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>876751</t>
+          <t>733642</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>754114</t>
+          <t>697805</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>1165183</t>
+          <t>767634</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>43,13%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>47,44%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6021,32 +6021,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>1841278</t>
+          <t>1513856</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>1606545</t>
+          <t>1460505</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>2231183</t>
+          <t>1567867</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>44,57%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>65,13%</t>
+          <t>47,85%</t>
         </is>
       </c>
     </row>
@@ -6064,17 +6064,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>1758661</t>
+          <t>1658938</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>1758661</t>
+          <t>1658938</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>1758661</t>
+          <t>1658938</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6099,17 +6099,17 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>1667306</t>
+          <t>1617978</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>1667306</t>
+          <t>1617978</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>1667306</t>
+          <t>1617978</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6134,17 +6134,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>3425967</t>
+          <t>3276916</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>3425967</t>
+          <t>3276916</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>3425967</t>
+          <t>3276916</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">

--- a/data/trans_orig/P41E_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P41E_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si con respecto al último año sus relaciones sexuales han sido satisfactorias para ambas partes en 2023 (tasa de respuesta: 69,32%)</t>
+          <t>Población según su nivel de acuerdo sobre la satisfacción de sus relaciones sexuales por ambas partes en el último mes en 2023 (tasa de respuesta: 69,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
